--- a/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0001T0006Z000C1N11_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0001T0006Z000C1N11_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>63.55012845056161</v>
+        <v>10.32689587321626</v>
       </c>
       <c r="D2" t="n">
-        <v>62.2330478315964</v>
+        <v>10.11287027263442</v>
       </c>
       <c r="E2" t="n">
-        <v>1.914798858534109</v>
+        <v>0.3111548145117933</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9451907790997787</v>
+        <v>0.153593501603714</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>59.72053073349339</v>
+        <v>9.704586244192676</v>
       </c>
       <c r="D3" t="n">
-        <v>60.34266627339684</v>
+        <v>9.805683269426988</v>
       </c>
       <c r="E3" t="n">
-        <v>1.914798858534109</v>
+        <v>0.3111548145117933</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9451907790997787</v>
+        <v>0.153593501603714</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
